--- a/public/downloads/MichalLixCoO22017.xlsx
+++ b/public/downloads/MichalLixCoO22017.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,13 +169,34 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>OOH</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>O</t>
   </si>
   <si>
     <t>OH</t>
+  </si>
+  <si>
+    <t>OOH</t>
   </si>
 </sst>
 </file>
@@ -659,10 +682,10 @@
         <v>15</v>
       </c>
       <c r="N3" s="5">
-        <v>117.4098596572876</v>
+        <v>117409.8596572876</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03533248861188312</v>
+        <v>35.33248861188311</v>
       </c>
       <c r="P3" s="5">
         <v>3323</v>
@@ -709,10 +732,10 @@
         <v>15</v>
       </c>
       <c r="N4" s="5">
-        <v>504.4122502803802</v>
+        <v>504412.2502803802</v>
       </c>
       <c r="O4" s="4">
-        <v>0.108732970528213</v>
+        <v>108.732970528213</v>
       </c>
       <c r="P4" s="5">
         <v>4639</v>
@@ -759,10 +782,10 @@
         <v>15</v>
       </c>
       <c r="N5" s="5">
-        <v>1857.436026334763</v>
+        <v>1857436.026334763</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1393007369382603</v>
+        <v>139.3007369382603</v>
       </c>
       <c r="P5" s="5">
         <v>13334</v>
@@ -809,10 +832,10 @@
         <v>15</v>
       </c>
       <c r="N6" s="5">
-        <v>496.3057043552399</v>
+        <v>496305.7043552399</v>
       </c>
       <c r="O6" s="4">
-        <v>0.1059576653192229</v>
+        <v>105.9576653192229</v>
       </c>
       <c r="P6" s="5">
         <v>4684</v>
@@ -859,10 +882,10 @@
         <v>15</v>
       </c>
       <c r="N7" s="5">
-        <v>1752.219300985336</v>
+        <v>1752219.300985336</v>
       </c>
       <c r="O7" s="4">
-        <v>0.4817759969714975</v>
+        <v>481.7759969714975</v>
       </c>
       <c r="P7" s="5">
         <v>3637</v>
@@ -909,10 +932,10 @@
         <v>15</v>
       </c>
       <c r="N8" s="5">
-        <v>116.5789277553558</v>
+        <v>116578.9277553558</v>
       </c>
       <c r="O8" s="4">
-        <v>0.03332730924967291</v>
+        <v>33.32730924967291</v>
       </c>
       <c r="P8" s="5">
         <v>3498</v>
@@ -959,10 +982,10 @@
         <v>15</v>
       </c>
       <c r="N9" s="5">
-        <v>252.4082231521606</v>
+        <v>252408.2231521606</v>
       </c>
       <c r="O9" s="4">
-        <v>0.04048896746104598</v>
+        <v>40.48896746104598</v>
       </c>
       <c r="P9" s="5">
         <v>6234</v>
@@ -1009,10 +1032,10 @@
         <v>15</v>
       </c>
       <c r="N10" s="5">
-        <v>214.3042666912079</v>
+        <v>214304.2666912079</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08450483702334696</v>
+        <v>84.50483702334697</v>
       </c>
       <c r="P10" s="5">
         <v>2536</v>
@@ -1059,10 +1082,10 @@
         <v>15</v>
       </c>
       <c r="N11" s="5">
-        <v>376.9542429447174</v>
+        <v>376954.2429447174</v>
       </c>
       <c r="O11" s="4">
-        <v>0.05615287396763256</v>
+        <v>56.15287396763257</v>
       </c>
       <c r="P11" s="5">
         <v>6713</v>
@@ -1109,10 +1132,10 @@
         <v>15</v>
       </c>
       <c r="N12" s="5">
-        <v>95.94815993309021</v>
+        <v>95948.15993309021</v>
       </c>
       <c r="O12" s="4">
-        <v>0.0321111646362417</v>
+        <v>32.1111646362417</v>
       </c>
       <c r="P12" s="5">
         <v>2988</v>
@@ -1159,10 +1182,10 @@
         <v>15</v>
       </c>
       <c r="N13" s="5">
-        <v>304.6261179447174</v>
+        <v>304626.1179447174</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07608044903714221</v>
+        <v>76.08044903714222</v>
       </c>
       <c r="P13" s="5">
         <v>4004</v>
@@ -1209,10 +1232,10 @@
         <v>15</v>
       </c>
       <c r="N14" s="5">
-        <v>5375.825808286667</v>
+        <v>5375825.808286667</v>
       </c>
       <c r="O14" s="4">
-        <v>0.7115586774701081</v>
+        <v>711.5586774701081</v>
       </c>
       <c r="P14" s="5">
         <v>7555</v>
@@ -1259,10 +1282,10 @@
         <v>15</v>
       </c>
       <c r="N15" s="5">
-        <v>2191.952303171158</v>
+        <v>2191952.303171158</v>
       </c>
       <c r="O15" s="4">
-        <v>0.6690941096371056</v>
+        <v>669.0941096371056</v>
       </c>
       <c r="P15" s="5">
         <v>3276</v>
@@ -1309,10 +1332,10 @@
         <v>15</v>
       </c>
       <c r="N16" s="5">
-        <v>1345.400872707367</v>
+        <v>1345400.872707367</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1405558788871048</v>
+        <v>140.5558788871048</v>
       </c>
       <c r="P16" s="5">
         <v>9572</v>
@@ -1359,10 +1382,10 @@
         <v>15</v>
       </c>
       <c r="N17" s="5">
-        <v>387.5634300708771</v>
+        <v>387563.4300708771</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1257506262397395</v>
+        <v>125.7506262397395</v>
       </c>
       <c r="P17" s="5">
         <v>3082</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,132 +1497,198 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2170077005315018</v>
+        <v>0.2952545162715355</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2764548647493864</v>
+        <v>0.3507032906513311</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3044343863060319</v>
+        <v>0.3409667716727617</v>
       </c>
       <c r="E3" s="4">
-        <v>88.21088435374151</v>
+        <v>85.53061224489795</v>
       </c>
       <c r="F3" s="4">
-        <v>71.76733780760632</v>
+        <v>75.8255033557047</v>
       </c>
       <c r="G3" s="5">
         <v>5</v>
       </c>
       <c r="H3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>4</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2952545162715355</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3507032906513311</v>
+      </c>
+      <c r="R3" s="5">
+        <v>4</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3651627150857376</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.4105068784786867</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3918478400465298</v>
+      </c>
+      <c r="E4" s="4">
+        <v>85.73469387755102</v>
+      </c>
+      <c r="F4" s="4">
+        <v>76.35570469798658</v>
+      </c>
+      <c r="G4" s="5">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3651627150857376</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4105068784786867</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.616786049167188</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.7269444633338837</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.6915584367861221</v>
+      </c>
+      <c r="E5" s="4">
+        <v>79.85714285714286</v>
+      </c>
+      <c r="F5" s="4">
+        <v>57.8993288590604</v>
+      </c>
+      <c r="G5" s="5">
+        <v>5</v>
+      </c>
+      <c r="H5" s="5">
         <v>2</v>
       </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
         <v>2</v>
       </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2429135449587072</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1768403186945915</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.204809968619727</v>
-      </c>
-      <c r="E4" s="4">
-        <v>91.59183673469387</v>
-      </c>
-      <c r="F4" s="4">
-        <v>81.75167785234905</v>
-      </c>
-      <c r="G4" s="5">
-        <v>5</v>
-      </c>
-      <c r="H4" s="5">
-        <v>3</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
         <v>2</v>
       </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
         <v>2</v>
       </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.2149373752913109</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.1978558411928348</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.1737068575960095</v>
-      </c>
-      <c r="E5" s="4">
-        <v>92.36734693877551</v>
-      </c>
-      <c r="F5" s="4">
-        <v>85.93959731543625</v>
-      </c>
-      <c r="G5" s="5">
-        <v>5</v>
-      </c>
-      <c r="H5" s="5">
-        <v>4</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
+      <c r="P5" s="4">
+        <v>0.616786049167188</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7269444633338837</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1699,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1707,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1718,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1760,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,132 +1791,198 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.36993593034668</v>
+        <v>0.7046871672539063</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.6586236013216147</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5951309258488769</v>
+        <v>0.7133914481071779</v>
       </c>
       <c r="E3" s="4">
-        <v>75.91156462585032</v>
+        <v>72.16326530612245</v>
       </c>
       <c r="F3" s="4">
-        <v>46.83668903803133</v>
+        <v>55.41163310961969</v>
       </c>
       <c r="G3" s="5">
         <v>5</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7046871672539063</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6586236013216147</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4736347685722658</v>
+        <v>0.4895374773046875</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5048487646191407</v>
+        <v>0.4839429298567708</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4755041609672853</v>
+        <v>0.4860750196478271</v>
       </c>
       <c r="E4" s="4">
-        <v>86.50340136054423</v>
+        <v>71.7006802721088</v>
       </c>
       <c r="F4" s="4">
-        <v>76.83892617449661</v>
+        <v>56.77628635346748</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
       </c>
       <c r="H4" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4895374773046875</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4839429298567708</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2830307481787109</v>
+        <v>1.342324302410156</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2830307481787109</v>
+        <v>1.321664021230469</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2813247201940918</v>
+        <v>0.8658996159581299</v>
       </c>
       <c r="E5" s="4">
-        <v>88.68707482993197</v>
+        <v>62.79591836734695</v>
       </c>
       <c r="F5" s="4">
-        <v>83.07606263982103</v>
+        <v>36.32214765100672</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
       </c>
       <c r="H5" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.342324302410156</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.321664021230469</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +1993,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2001,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2012,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2054,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,34 +2085,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5530914434312744</v>
+        <v>0.2429135449587072</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1499432070312499</v>
+        <v>0.1768403186945915</v>
       </c>
       <c r="D3" s="4">
-        <v>0.137483437086792</v>
+        <v>0.204809968619727</v>
       </c>
       <c r="E3" s="4">
-        <v>83.93197278911558</v>
+        <v>91.59183673469387</v>
       </c>
       <c r="F3" s="4">
-        <v>59.85906040268441</v>
+        <v>81.75167785234905</v>
       </c>
       <c r="G3" s="5">
         <v>5</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>2</v>
@@ -1927,66 +2144,98 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2429135449587072</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1768403186945915</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2338346014885255</v>
+        <v>0.2149373752913109</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1569869372489422</v>
+        <v>0.1978558411928348</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2600692282585451</v>
+        <v>0.1737068575960095</v>
       </c>
       <c r="E4" s="4">
-        <v>91.55782312925169</v>
+        <v>92.36734693877551</v>
       </c>
       <c r="F4" s="4">
-        <v>79.1789709172261</v>
+        <v>85.93959731543625</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
       </c>
       <c r="H4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2149373752913109</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1978558411928348</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2018999601143799</v>
+        <v>0.2170077005315018</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1506178051645915</v>
+        <v>0.2764548647493864</v>
       </c>
       <c r="D5" s="4">
-        <v>0.08737880156774903</v>
+        <v>0.3044343863060319</v>
       </c>
       <c r="E5" s="4">
-        <v>91.08163265306122</v>
+        <v>88.21088435374151</v>
       </c>
       <c r="F5" s="4">
-        <v>80.53467561521281</v>
+        <v>71.76733780760632</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
@@ -2009,9 +2258,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2170077005315018</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2764548647493864</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2287,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2295,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2306,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2348,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,132 +2379,196 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2177390318033448</v>
+        <v>0.4736347685722658</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5676941134698485</v>
+        <v>0.5048487646191407</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3105214173344726</v>
+        <v>0.4755041609672853</v>
       </c>
       <c r="E3" s="4">
-        <v>76.31972789115648</v>
+        <v>86.50340136054423</v>
       </c>
       <c r="F3" s="4">
-        <v>52.23489932885906</v>
+        <v>76.83892617449661</v>
       </c>
       <c r="G3" s="5">
         <v>5</v>
       </c>
       <c r="H3" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>4</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4736347685722658</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5048487646191407</v>
+      </c>
+      <c r="R3" s="5">
+        <v>4</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2749385128444825</v>
+        <v>0.2830307481787109</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2685255063814291</v>
+        <v>0.2830307481787109</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2873674879936525</v>
+        <v>0.2813247201940918</v>
       </c>
       <c r="E4" s="4">
-        <v>81.70748299319729</v>
+        <v>88.68707482993197</v>
       </c>
       <c r="F4" s="4">
-        <v>66.07158836689038</v>
+        <v>83.07606263982103</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
       </c>
       <c r="H4" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2830307481787109</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.16435170415625</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.16435170415625</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1560821103155518</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.1656320105819702</v>
-      </c>
+        <v>1.36993593034668</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.1278792428076172</v>
+        <v>0.5951309258488769</v>
       </c>
       <c r="E5" s="4">
-        <v>81.11564625850338</v>
+        <v>75.91156462585032</v>
       </c>
       <c r="F5" s="4">
-        <v>72.99552572706932</v>
+        <v>46.83668903803133</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
       </c>
       <c r="H5" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.36993593034668</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2579,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2587,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2598,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2640,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,107 +2671,157 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5880223869137045</v>
+        <v>0.2338346014885255</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5707443513635249</v>
+        <v>0.1569869372489422</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3282680672661322</v>
+        <v>0.2600692282585451</v>
       </c>
       <c r="E3" s="4">
-        <v>67.4829931972789</v>
+        <v>91.55782312925169</v>
       </c>
       <c r="F3" s="4">
-        <v>39.3937360178971</v>
+        <v>79.1789709172261</v>
       </c>
       <c r="G3" s="5">
         <v>5</v>
       </c>
       <c r="H3" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2338346014885255</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1569869372489422</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.8170239081391102</v>
+        <v>0.2018999601143799</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3012233635463311</v>
+        <v>0.1506178051645915</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2969627013213355</v>
+        <v>0.08737880156774903</v>
       </c>
       <c r="E4" s="4">
-        <v>68.48979591836735</v>
+        <v>91.08163265306122</v>
       </c>
       <c r="F4" s="4">
-        <v>44.51230425055925</v>
+        <v>80.53467561521281</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2018999601143799</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1506178051645915</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2060410862902803</v>
+        <v>0.5530914434312744</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1933856996484091</v>
+        <v>0.1499432070312499</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1674062544840065</v>
+        <v>0.137483437086792</v>
       </c>
       <c r="E5" s="4">
-        <v>70.93197278911565</v>
+        <v>83.93197278911558</v>
       </c>
       <c r="F5" s="4">
-        <v>57.50782997762864</v>
+        <v>59.85906040268441</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
@@ -2421,23 +2830,39 @@
         <v>2</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5530914434312744</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1499432070312499</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2873,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2881,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2892,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2934,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,25 +2965,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7220393782109789</v>
+        <v>0.2749385128444825</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3426665722890882</v>
+        <v>0.2685255063814291</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3196626906841623</v>
+        <v>0.2873674879936525</v>
       </c>
       <c r="E3" s="4">
-        <v>80.25850340136057</v>
+        <v>81.70748299319729</v>
       </c>
       <c r="F3" s="4">
-        <v>68.61968680089443</v>
+        <v>66.07158836689038</v>
       </c>
       <c r="G3" s="5">
         <v>5</v>
@@ -2566,25 +3024,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2749385128444825</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2685255063814291</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1144317915448157</v>
+        <v>0.1560821103155518</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1014246583117351</v>
+        <v>0.1656320105819702</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1270753568547947</v>
+        <v>0.1278792428076172</v>
       </c>
       <c r="E4" s="4">
-        <v>84.72789115646259</v>
+        <v>81.11564625850338</v>
       </c>
       <c r="F4" s="4">
-        <v>80.79194630872431</v>
+        <v>72.99552572706932</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
@@ -2607,50 +3081,82 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1560821103155518</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1656320105819702</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2966074885824831</v>
+        <v>0.2177390318033448</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3140132551809956</v>
+        <v>0.5676941134698485</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3100274147486765</v>
+        <v>0.3105214173344726</v>
       </c>
       <c r="E5" s="4">
-        <v>85.89115646258504</v>
+        <v>76.31972789115648</v>
       </c>
       <c r="F5" s="4">
-        <v>84.4138702460845</v>
+        <v>52.23489932885906</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
       </c>
       <c r="H5" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2177390318033448</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5676941134698485</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3167,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3175,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3186,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3228,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,107 +3259,157 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6473123221446972</v>
+        <v>0.8170239081391102</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.3012233635463311</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3734297659082924</v>
+        <v>0.2969627013213355</v>
       </c>
       <c r="E3" s="4">
-        <v>33.06802721088435</v>
+        <v>68.48979591836735</v>
       </c>
       <c r="F3" s="4">
-        <v>25.61521252796419</v>
+        <v>44.51230425055925</v>
       </c>
       <c r="G3" s="5">
         <v>5</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>4</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8170239081391102</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3012233635463311</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6194402625563541</v>
+        <v>0.2060410862902803</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>0.1933856996484091</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3061162760701164</v>
+        <v>0.1674062544840065</v>
       </c>
       <c r="E4" s="4">
-        <v>29.04761904761905</v>
+        <v>70.93197278911565</v>
       </c>
       <c r="F4" s="4">
-        <v>21.66219239373602</v>
+        <v>57.50782997762864</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2060410862902803</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1933856996484091</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.300080704454336</v>
+        <v>0.5880223869137045</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4922131341881027</v>
+        <v>0.5707443513635249</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2822685567175025</v>
+        <v>0.3282680672661322</v>
       </c>
       <c r="E5" s="4">
-        <v>35.41496598639456</v>
+        <v>67.4829931972789</v>
       </c>
       <c r="F5" s="4">
-        <v>35.68903803131991</v>
+        <v>39.3937360178971</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
@@ -2853,17 +3424,33 @@
         <v>4</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5880223869137045</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5707443513635249</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3461,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3469,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3480,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3522,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,34 +3553,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5397208937522346</v>
+        <v>0.1144317915448157</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1410459767972664</v>
+        <v>0.1014246583117351</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1043764143043419</v>
+        <v>0.1270753568547947</v>
       </c>
       <c r="E3" s="4">
-        <v>83.76190476190474</v>
+        <v>84.72789115646259</v>
       </c>
       <c r="F3" s="4">
-        <v>69.14093959731544</v>
+        <v>80.79194630872431</v>
       </c>
       <c r="G3" s="5">
         <v>5</v>
       </c>
       <c r="H3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>1</v>
@@ -2992,91 +3612,139 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>4</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1144317915448157</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1014246583117351</v>
+      </c>
+      <c r="R3" s="5">
+        <v>4</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1623603394038144</v>
+        <v>0.2966074885824831</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1623603394038144</v>
+        <v>0.3140132551809956</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1455152323252735</v>
+        <v>0.3100274147486765</v>
       </c>
       <c r="E4" s="4">
-        <v>87.97278911564626</v>
+        <v>85.89115646258504</v>
       </c>
       <c r="F4" s="4">
-        <v>84.27069351230428</v>
+        <v>84.4138702460845</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
       </c>
       <c r="H4" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2966074885824831</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3140132551809956</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1837586904304326</v>
+        <v>0.7220393782109789</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1837586904304326</v>
+        <v>0.3426665722890882</v>
       </c>
       <c r="D5" s="4">
-        <v>0.15577474851357</v>
+        <v>0.3196626906841623</v>
       </c>
       <c r="E5" s="4">
-        <v>88.06122448979592</v>
+        <v>80.25850340136057</v>
       </c>
       <c r="F5" s="4">
-        <v>86.39597315436242</v>
+        <v>68.61968680089443</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
       </c>
       <c r="H5" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7220393782109789</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3426665722890882</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3755,1454 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.6194402625563541</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
+        <v>0.3061162760701164</v>
+      </c>
+      <c r="E3" s="4">
+        <v>29.04761904761905</v>
+      </c>
+      <c r="F3" s="4">
+        <v>21.66219239373602</v>
+      </c>
+      <c r="G3" s="5">
+        <v>5</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>5</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>5</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6194402625563541</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.300080704454336</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.4922131341881027</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2822685567175025</v>
+      </c>
+      <c r="E4" s="4">
+        <v>35.41496598639456</v>
+      </c>
+      <c r="F4" s="4">
+        <v>35.68903803131991</v>
+      </c>
+      <c r="G4" s="5">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>4</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.300080704454336</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4922131341881027</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.6473123221446972</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
+        <v>0.3734297659082924</v>
+      </c>
+      <c r="E5" s="4">
+        <v>33.06802721088435</v>
+      </c>
+      <c r="F5" s="4">
+        <v>25.61521252796419</v>
+      </c>
+      <c r="G5" s="5">
+        <v>5</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>4</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>4</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6473123221446972</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.1623603394038144</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.1623603394038144</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.1455152323252735</v>
+      </c>
+      <c r="E3" s="4">
+        <v>87.97278911564626</v>
+      </c>
+      <c r="F3" s="4">
+        <v>84.27069351230428</v>
+      </c>
+      <c r="G3" s="5">
+        <v>5</v>
+      </c>
+      <c r="H3" s="5">
+        <v>5</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.005845569524253413</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1611912254989637</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1611912254989637</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1837586904304326</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1837586904304326</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.15577474851357</v>
+      </c>
+      <c r="E4" s="4">
+        <v>88.06122448979592</v>
+      </c>
+      <c r="F4" s="4">
+        <v>86.39597315436242</v>
+      </c>
+      <c r="G4" s="5">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5">
+        <v>5</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.1712827684383477</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.149502136742763</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.149502136742763</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.5397208937522346</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1410459767972664</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.1043764143043419</v>
+      </c>
+      <c r="E5" s="4">
+        <v>83.76190476190474</v>
+      </c>
+      <c r="F5" s="4">
+        <v>69.14093959731544</v>
+      </c>
+      <c r="G5" s="5">
+        <v>5</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5397208937522346</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1410459767972664</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="C3" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="D3" s="3">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>20</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.4001096696137695</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.3953974520627664</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.4139500075437825</v>
+      </c>
+      <c r="K3" s="4">
+        <v>82.15419501133789</v>
+      </c>
+      <c r="L3" s="4">
+        <v>74.54511558538314</v>
+      </c>
+      <c r="M3" s="5">
+        <v>15</v>
+      </c>
+      <c r="N3" s="5">
+        <v>117409.8596572876</v>
+      </c>
+      <c r="O3" s="4">
+        <v>35.33248861188311</v>
+      </c>
+      <c r="P3" s="5">
+        <v>3323</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="C4" s="3">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="D4" s="3">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="G4" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1.096646983154948</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.3667177111240235</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1.294910051535156</v>
+      </c>
+      <c r="K4" s="4">
+        <v>80.56235827664398</v>
+      </c>
+      <c r="L4" s="4">
+        <v>65.22520507084292</v>
+      </c>
+      <c r="M4" s="5">
+        <v>15</v>
+      </c>
+      <c r="N4" s="5">
+        <v>504412.2502803802</v>
+      </c>
+      <c r="O4" s="4">
+        <v>108.732970528213</v>
+      </c>
+      <c r="P4" s="5">
+        <v>4639</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>40</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>60</v>
+      </c>
+      <c r="E5" s="3">
+        <v>20</v>
+      </c>
+      <c r="F5" s="3">
+        <v>40</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.3651675288858008</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.3105810370273893</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.290284894268301</v>
+      </c>
+      <c r="K5" s="4">
+        <v>80.82312925170091</v>
+      </c>
+      <c r="L5" s="4">
+        <v>56.65249813572034</v>
+      </c>
+      <c r="M5" s="5">
+        <v>15</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1857436.026334763</v>
+      </c>
+      <c r="O5" s="4">
+        <v>139.3007369382603</v>
+      </c>
+      <c r="P5" s="5">
+        <v>13334</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.4128488775586752</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.4057610059993199</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.4326485654816895</v>
+      </c>
+      <c r="K6" s="4">
+        <v>70.56009070294813</v>
+      </c>
+      <c r="L6" s="4">
+        <v>54.08202833706208</v>
+      </c>
+      <c r="M6" s="5">
+        <v>15</v>
+      </c>
+      <c r="N6" s="5">
+        <v>496305.7043552399</v>
+      </c>
+      <c r="O6" s="4">
+        <v>105.9576653192229</v>
+      </c>
+      <c r="P6" s="5">
+        <v>4684</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="C7" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="D7" s="3">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.3752083218590088</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.286068810909729</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.3079543134675293</v>
+      </c>
+      <c r="K7" s="4">
+        <v>83.84126984126992</v>
+      </c>
+      <c r="L7" s="4">
+        <v>70.52274422072998</v>
+      </c>
+      <c r="M7" s="5">
+        <v>15</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1752219.300985336</v>
+      </c>
+      <c r="O7" s="4">
+        <v>481.7759969714975</v>
+      </c>
+      <c r="P7" s="5">
+        <v>3637</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="C8" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="D8" s="3">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.4257344268414871</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.4498729603187838</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.4747910161684711</v>
+      </c>
+      <c r="K8" s="4">
+        <v>83.70748299319737</v>
+      </c>
+      <c r="L8" s="4">
+        <v>70.02684563758385</v>
+      </c>
+      <c r="M8" s="5">
+        <v>15</v>
+      </c>
+      <c r="N8" s="5">
+        <v>116578.9277553558</v>
+      </c>
+      <c r="O8" s="4">
+        <v>33.32730924967291</v>
+      </c>
+      <c r="P8" s="5">
+        <v>3498</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="F9" s="3">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.8455163156562501</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.6784805163950894</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.6884553612377116</v>
+      </c>
+      <c r="K9" s="4">
+        <v>68.88662131519276</v>
+      </c>
+      <c r="L9" s="4">
+        <v>49.50335570469765</v>
+      </c>
+      <c r="M9" s="5">
+        <v>15</v>
+      </c>
+      <c r="N9" s="5">
+        <v>252408.2231521606</v>
+      </c>
+      <c r="O9" s="4">
+        <v>40.48896746104598</v>
+      </c>
+      <c r="P9" s="5">
+        <v>6234</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.22495287359384</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.2151308915103272</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.2276504041739228</v>
+      </c>
+      <c r="K10" s="4">
+        <v>90.72335600907029</v>
+      </c>
+      <c r="L10" s="4">
+        <v>79.81953765846403</v>
+      </c>
+      <c r="M10" s="5">
+        <v>15</v>
+      </c>
+      <c r="N10" s="5">
+        <v>214304.2666912079</v>
+      </c>
+      <c r="O10" s="4">
+        <v>84.50483702334697</v>
+      </c>
+      <c r="P10" s="5">
+        <v>2536</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>60</v>
+      </c>
+      <c r="C11" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="D11" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="E11" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="F11" s="3">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.6693074676917318</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.3156837310286459</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.3989154845335288</v>
+      </c>
+      <c r="K11" s="4">
+        <v>83.70068027210911</v>
+      </c>
+      <c r="L11" s="4">
+        <v>68.91722595078434</v>
+      </c>
+      <c r="M11" s="5">
+        <v>15</v>
+      </c>
+      <c r="N11" s="5">
+        <v>376954.2429447174</v>
+      </c>
+      <c r="O11" s="4">
+        <v>56.15287396763257</v>
+      </c>
+      <c r="P11" s="5">
+        <v>6713</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="C12" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="D12" s="3">
+        <v>40</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>40</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.3296086683447266</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1528375801628876</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1616438223043621</v>
+      </c>
+      <c r="K12" s="4">
+        <v>88.85714285714283</v>
+      </c>
+      <c r="L12" s="4">
+        <v>73.19090231170816</v>
+      </c>
+      <c r="M12" s="5">
+        <v>15</v>
+      </c>
+      <c r="N12" s="5">
+        <v>95948.15993309021</v>
+      </c>
+      <c r="O12" s="4">
+        <v>32.1111646362417</v>
+      </c>
+      <c r="P12" s="5">
+        <v>2988</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="C13" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="D13" s="3">
+        <v>40</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>40</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.2162532183211264</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.2544748343677521</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2419227160452475</v>
+      </c>
+      <c r="K13" s="4">
+        <v>79.71428571428568</v>
+      </c>
+      <c r="L13" s="4">
+        <v>63.76733780760645</v>
+      </c>
+      <c r="M13" s="5">
+        <v>15</v>
+      </c>
+      <c r="N13" s="5">
+        <v>304626.1179447174</v>
+      </c>
+      <c r="O13" s="4">
+        <v>76.08044903714222</v>
+      </c>
+      <c r="P13" s="5">
+        <v>4004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="F14" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.537029127114365</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.3146847785516685</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.2642123410238247</v>
+      </c>
+      <c r="K14" s="4">
+        <v>68.96825396825396</v>
+      </c>
+      <c r="L14" s="4">
+        <v>47.13795674869487</v>
+      </c>
+      <c r="M14" s="5">
+        <v>15</v>
+      </c>
+      <c r="N14" s="5">
+        <v>5375825.808286667</v>
+      </c>
+      <c r="O14" s="4">
+        <v>711.5586774701081</v>
+      </c>
+      <c r="P14" s="5">
+        <v>7555</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.3776928861127593</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2445228518943806</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2522551540958778</v>
+      </c>
+      <c r="K15" s="4">
+        <v>83.62585034013605</v>
+      </c>
+      <c r="L15" s="4">
+        <v>77.94183445189935</v>
+      </c>
+      <c r="M15" s="5">
+        <v>15</v>
+      </c>
+      <c r="N15" s="5">
+        <v>2191952.303171158</v>
+      </c>
+      <c r="O15" s="4">
+        <v>669.0941096371056</v>
+      </c>
+      <c r="P15" s="5">
+        <v>3276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="C16" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="D16" s="3">
+        <v>86.66666666666667</v>
+      </c>
+      <c r="E16" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="F16" s="3">
+        <v>80</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.5222777630517957</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.4922131341881027</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.3206048662319704</v>
+      </c>
+      <c r="K16" s="4">
+        <v>32.51020408163266</v>
+      </c>
+      <c r="L16" s="4">
+        <v>27.6554809843401</v>
+      </c>
+      <c r="M16" s="5">
+        <v>15</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1345400.872707367</v>
+      </c>
+      <c r="O16" s="4">
+        <v>140.5558788871048</v>
+      </c>
+      <c r="P16" s="5">
+        <v>9572</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>86.66666666666667</v>
+      </c>
+      <c r="C17" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="D17" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.2834714186646538</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.1520465185846487</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.1178298770621726</v>
+      </c>
+      <c r="K17" s="4">
+        <v>86.59863945578228</v>
+      </c>
+      <c r="L17" s="4">
+        <v>79.93586875465932</v>
+      </c>
+      <c r="M17" s="5">
+        <v>15</v>
+      </c>
+      <c r="N17" s="5">
+        <v>387563.4300708771</v>
+      </c>
+      <c r="O17" s="4">
+        <v>125.7506262397395</v>
+      </c>
+      <c r="P17" s="5">
+        <v>3082</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3297,13 +5407,13 @@
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
       <c r="N5" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -3473,7 +5583,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
@@ -3558,10 +5668,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
@@ -3693,13 +5803,13 @@
         <v>0</v>
       </c>
       <c r="L14" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
       </c>
       <c r="N14" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="25" customHeight="1">
@@ -3781,13 +5891,13 @@
         <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -3847,9 +5957,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>11</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>3</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5">
+        <v>8</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>7</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>5</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>6</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5">
+        <v>3</v>
+      </c>
+      <c r="F5" s="5">
+        <v>6</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>4</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>7</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>8</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>8</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>8</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>10</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>4</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>3</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>4</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>4</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>7</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>8</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <v>7</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5">
+        <v>1</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>7</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>5</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>5</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>2</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>5</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5">
+        <v>4</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5">
+        <v>1</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>4</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>6</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>6</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>4</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>6</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>6</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>6</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>4</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>11</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5">
+        <v>10</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5">
+        <v>1</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>8</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>4</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>4</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>3</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
+        <v>13</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5">
+        <v>12</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>12</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>13</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>1</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6725,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6767,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,132 +6798,200 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.4142915444501954</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.5123516449951173</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3989813338188478</v>
+      </c>
+      <c r="E3" s="4">
+        <v>84.33333333333333</v>
+      </c>
+      <c r="F3" s="4">
+        <v>82.31543624161068</v>
+      </c>
+      <c r="G3" s="5">
+        <v>5</v>
+      </c>
+      <c r="H3" s="5">
+        <v>4</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>4</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4142915444501954</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5123516449951173</v>
+      </c>
+      <c r="R3" s="5">
+        <v>4</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3165243623754883</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3165243623754883</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2828723428747558</v>
+      </c>
+      <c r="E4" s="4">
+        <v>83.54421768707483</v>
+      </c>
+      <c r="F4" s="4">
+        <v>81.64429530201342</v>
+      </c>
+      <c r="G4" s="5">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5">
+        <v>5</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.3165243623754883</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.158558247125</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.158558247125</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.6274792172661132</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C5" s="4">
         <v>0.7535870785424805</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D5" s="4">
         <v>0.6931659752873535</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E5" s="4">
         <v>78.58503401360545</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F5" s="4">
         <v>59.67561521252795</v>
       </c>
-      <c r="G3" s="5">
-        <v>5</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="G5" s="5">
+        <v>5</v>
+      </c>
+      <c r="H5" s="5">
         <v>2</v>
       </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
         <v>2</v>
       </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
         <v>2</v>
       </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.4142915444501954</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.5123516449951173</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3989813338188478</v>
-      </c>
-      <c r="E4" s="4">
-        <v>84.33333333333333</v>
-      </c>
-      <c r="F4" s="4">
-        <v>82.31543624161068</v>
-      </c>
-      <c r="G4" s="5">
-        <v>5</v>
-      </c>
-      <c r="H4" s="5">
-        <v>4</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.3165243623754883</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3165243623754883</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.2828723428747558</v>
-      </c>
-      <c r="E5" s="4">
-        <v>83.54421768707483</v>
-      </c>
-      <c r="F5" s="4">
-        <v>81.64429530201342</v>
-      </c>
-      <c r="G5" s="5">
-        <v>5</v>
-      </c>
-      <c r="H5" s="5">
-        <v>5</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6274792172661132</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7535870785424805</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7002,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7021,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7063,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,132 +7094,194 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.4661232481865236</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.7294818421875</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.5982292662529298</v>
+      </c>
+      <c r="E3" s="4">
+        <v>83.37414965986393</v>
+      </c>
+      <c r="F3" s="4">
+        <v>70.1565995525727</v>
+      </c>
+      <c r="G3" s="5">
+        <v>5</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>2</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4661232481865236</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7294818421875</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3472287790610352</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2760266783581543</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2961096284887695</v>
+      </c>
+      <c r="E4" s="4">
+        <v>86.27210884353742</v>
+      </c>
+      <c r="F4" s="4">
+        <v>77.13870246085011</v>
+      </c>
+      <c r="G4" s="5">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3472287790610352</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2760266783581543</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>2.476588922217285</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
         <v>2.990391259863769</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E5" s="4">
         <v>72.04081632653062</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F5" s="4">
         <v>48.38031319910514</v>
       </c>
-      <c r="G3" s="5">
-        <v>5</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>5</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>4</v>
-      </c>
-      <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.4661232481865236</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.7294818421875</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.5982292662529298</v>
-      </c>
-      <c r="E4" s="4">
-        <v>83.37414965986393</v>
-      </c>
-      <c r="F4" s="4">
-        <v>70.1565995525727</v>
-      </c>
-      <c r="G4" s="5">
-        <v>5</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>2</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.3472287790610352</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2760266783581543</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.2961096284887695</v>
-      </c>
-      <c r="E5" s="4">
-        <v>86.27210884353742</v>
-      </c>
-      <c r="F5" s="4">
-        <v>77.13870246085011</v>
-      </c>
       <c r="G5" s="5">
         <v>5</v>
       </c>
       <c r="H5" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.476588922217285</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7292,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7311,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7353,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,132 +7384,198 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.4992019506224709</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4846328919568921</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.4580234776405641</v>
+      </c>
+      <c r="E3" s="4">
+        <v>78.64625850340154</v>
+      </c>
+      <c r="F3" s="4">
+        <v>53.41163310961969</v>
+      </c>
+      <c r="G3" s="5">
+        <v>5</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>3</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4992019506224709</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4846328919568921</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1437866786718273</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1668103298650583</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1271071923873329</v>
+      </c>
+      <c r="E4" s="4">
+        <v>85.28571428571421</v>
+      </c>
+      <c r="F4" s="4">
+        <v>67.28859060402593</v>
+      </c>
+      <c r="G4" s="5">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1437866786718273</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1668103298650583</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.452513957363104</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C5" s="4">
         <v>0.3937894486553764</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D5" s="4">
         <v>0.2857240127770061</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E5" s="4">
         <v>78.53741496598639</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F5" s="4">
         <v>49.2572706935119</v>
       </c>
-      <c r="G3" s="5">
-        <v>5</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>4</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>3</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.4992019506224709</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.4846328919568921</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.4580234776405641</v>
-      </c>
-      <c r="E4" s="4">
-        <v>78.64625850340154</v>
-      </c>
-      <c r="F4" s="4">
-        <v>53.41163310961969</v>
-      </c>
-      <c r="G4" s="5">
-        <v>5</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>3</v>
-      </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.1437866786718273</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.1668103298650583</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.1271071923873329</v>
-      </c>
-      <c r="E5" s="4">
-        <v>85.28571428571421</v>
-      </c>
-      <c r="F5" s="4">
-        <v>67.28859060402593</v>
-      </c>
       <c r="G5" s="5">
         <v>5</v>
       </c>
       <c r="H5" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5" s="5">
         <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.452513957363104</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3937894486553764</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7586,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7605,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7647,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,25 +7678,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4528696279642335</v>
+        <v>0.4952470312980958</v>
       </c>
       <c r="C3" s="4">
-        <v>0.580525469274292</v>
+        <v>0.3965015424230958</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5200739438084716</v>
+        <v>0.5052299033073732</v>
       </c>
       <c r="E3" s="4">
-        <v>66.95238095238096</v>
+        <v>74.50340136054423</v>
       </c>
       <c r="F3" s="4">
-        <v>45.46308724832213</v>
+        <v>58.24161073825503</v>
       </c>
       <c r="G3" s="5">
         <v>5</v>
@@ -4599,91 +7737,139 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4952470312980958</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3965015424230958</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4952470312980958</v>
+        <v>0.2904299734136963</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3965015424230958</v>
+        <v>0.295424339533488</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5052299033073732</v>
+        <v>0.2726418493292236</v>
       </c>
       <c r="E4" s="4">
-        <v>74.50340136054423</v>
+        <v>70.22448979591837</v>
       </c>
       <c r="F4" s="4">
-        <v>58.24161073825503</v>
+        <v>58.54138702460848</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
       </c>
       <c r="H4" s="5">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
         <v>2</v>
       </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>3</v>
-      </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2904299734136963</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.295424339533488</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2904299734136963</v>
+        <v>0.4528696279642335</v>
       </c>
       <c r="C5" s="4">
-        <v>0.295424339533488</v>
+        <v>0.580525469274292</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2726418493292236</v>
+        <v>0.5200739438084716</v>
       </c>
       <c r="E5" s="4">
-        <v>70.22448979591837</v>
+        <v>66.95238095238096</v>
       </c>
       <c r="F5" s="4">
-        <v>58.54138702460848</v>
+        <v>45.46308724832213</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
       </c>
       <c r="H5" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
         <v>2</v>
       </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
+      <c r="P5" s="4">
+        <v>0.4528696279642335</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.580525469274292</v>
+      </c>
+      <c r="R5" s="5">
         <v>2</v>
       </c>
-      <c r="M5" s="5">
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7880,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7899,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +7941,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,132 +7972,198 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.3043777953056642</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2493354718096925</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.269368887987549</v>
+      </c>
+      <c r="E3" s="4">
+        <v>85.99319727891157</v>
+      </c>
+      <c r="F3" s="4">
+        <v>76.420581655481</v>
+      </c>
+      <c r="G3" s="5">
+        <v>5</v>
+      </c>
+      <c r="H3" s="5">
+        <v>4</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>4</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3043777953056642</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2493354718096925</v>
+      </c>
+      <c r="R3" s="5">
+        <v>4</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2226052759191894</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.206727261302948</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1971542356512451</v>
+      </c>
+      <c r="E4" s="4">
+        <v>85.38095238095238</v>
+      </c>
+      <c r="F4" s="4">
+        <v>78.11185682326621</v>
+      </c>
+      <c r="G4" s="5">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2226052759191894</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.206727261302948</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.598641894352173</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C5" s="4">
         <v>0.5182185883233643</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D5" s="4">
         <v>0.4573398167637939</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E5" s="4">
         <v>80.14965986394559</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F5" s="4">
         <v>57.03579418344518</v>
       </c>
-      <c r="G3" s="5">
-        <v>5</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="G5" s="5">
+        <v>5</v>
+      </c>
+      <c r="H5" s="5">
         <v>2</v>
       </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
         <v>2</v>
       </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
         <v>2</v>
       </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3043777953056642</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2493354718096925</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.269368887987549</v>
-      </c>
-      <c r="E4" s="4">
-        <v>85.99319727891157</v>
-      </c>
-      <c r="F4" s="4">
-        <v>76.420581655481</v>
-      </c>
-      <c r="G4" s="5">
-        <v>5</v>
-      </c>
-      <c r="H4" s="5">
-        <v>4</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.2226052759191894</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.206727261302948</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.1971542356512451</v>
-      </c>
-      <c r="E5" s="4">
-        <v>85.38095238095238</v>
-      </c>
-      <c r="F5" s="4">
-        <v>78.11185682326621</v>
-      </c>
-      <c r="G5" s="5">
-        <v>5</v>
-      </c>
-      <c r="H5" s="5">
-        <v>4</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.598641894352173</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5182185883233643</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8174,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.616786049167188</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.7269444633338837</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.6915584367861221</v>
-      </c>
-      <c r="E3" s="4">
-        <v>79.85714285714286</v>
-      </c>
-      <c r="F3" s="4">
-        <v>57.8993288590604</v>
-      </c>
-      <c r="G3" s="5">
-        <v>5</v>
-      </c>
-      <c r="H3" s="5">
-        <v>2</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2952545162715355</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3507032906513311</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3409667716727617</v>
-      </c>
-      <c r="E4" s="4">
-        <v>85.53061224489795</v>
-      </c>
-      <c r="F4" s="4">
-        <v>75.8255033557047</v>
-      </c>
-      <c r="G4" s="5">
-        <v>5</v>
-      </c>
-      <c r="H4" s="5">
-        <v>4</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.3651627150857376</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.4105068784786867</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3918478400465298</v>
-      </c>
-      <c r="E5" s="4">
-        <v>85.73469387755102</v>
-      </c>
-      <c r="F5" s="4">
-        <v>76.35570469798658</v>
-      </c>
-      <c r="G5" s="5">
-        <v>5</v>
-      </c>
-      <c r="H5" s="5">
-        <v>4</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.342324302410156</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.321664021230469</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.8658996159581299</v>
-      </c>
-      <c r="E3" s="4">
-        <v>62.79591836734695</v>
-      </c>
-      <c r="F3" s="4">
-        <v>36.32214765100672</v>
-      </c>
-      <c r="G3" s="5">
-        <v>5</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>4</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>3</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.7046871672539063</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6586236013216147</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.7133914481071779</v>
-      </c>
-      <c r="E4" s="4">
-        <v>72.16326530612245</v>
-      </c>
-      <c r="F4" s="4">
-        <v>55.41163310961969</v>
-      </c>
-      <c r="G4" s="5">
-        <v>5</v>
-      </c>
-      <c r="H4" s="5">
-        <v>3</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.4895374773046875</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.4839429298567708</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.4860750196478271</v>
-      </c>
-      <c r="E5" s="4">
-        <v>71.7006802721088</v>
-      </c>
-      <c r="F5" s="4">
-        <v>56.77628635346748</v>
-      </c>
-      <c r="G5" s="5">
-        <v>5</v>
-      </c>
-      <c r="H5" s="5">
-        <v>3</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>2</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>2</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/MichalLixCoO22017.xlsx
+++ b/public/downloads/MichalLixCoO22017.xlsx
@@ -2496,16 +2496,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2830307481787109</v>
+        <v>0.172735072788086</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.16435170415625</v>
+        <v>0.142292569078125</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.16435170415625</v>
+        <v>0.142292569078125</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -4193,16 +4193,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.005845569524253413</v>
+        <v>-0.07834901758018331</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1611912254989637</v>
+        <v>0.1466905358877777</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1611912254989637</v>
+        <v>0.1466905358877777</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -4252,16 +4252,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1712827684383477</v>
+        <v>-0.2301030381367043</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.149502136742763</v>
+        <v>0.1377380828030917</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.149502136742763</v>
+        <v>0.1377380828030917</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -4455,13 +4455,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.4001096696137695</v>
+        <v>0.3977317497387695</v>
       </c>
       <c r="I3" s="4">
-        <v>0.3953974520627664</v>
+        <v>0.3921548340514028</v>
       </c>
       <c r="J3" s="4">
-        <v>0.4139500075437825</v>
+        <v>0.4115720876687826</v>
       </c>
       <c r="K3" s="4">
         <v>82.15419501133789</v>
@@ -4855,13 +4855,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.6693074676917318</v>
+        <v>0.6619544226656902</v>
       </c>
       <c r="I11" s="4">
-        <v>0.3156837310286459</v>
+        <v>0.3034286559852431</v>
       </c>
       <c r="J11" s="4">
-        <v>0.3989154845335288</v>
+        <v>0.3981858414615885</v>
       </c>
       <c r="K11" s="4">
         <v>83.70068027210911</v>
@@ -5155,13 +5155,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.2834714186646538</v>
+        <v>0.2747165041477013</v>
       </c>
       <c r="I17" s="4">
-        <v>0.1520465185846487</v>
+        <v>0.1419446941420112</v>
       </c>
       <c r="J17" s="4">
-        <v>0.1178298770621726</v>
+        <v>0.1149332660042025</v>
       </c>
       <c r="K17" s="4">
         <v>86.59863945578228</v>
@@ -6915,16 +6915,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3165243623754883</v>
+        <v>0.2808555642504883</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.158558247125</v>
+        <v>0.1514244875</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.158558247125</v>
+        <v>0.1514244875</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
